--- a/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
+++ b/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9994D786-B0F3-4ED2-A571-B60413F9EDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AC5C83-030E-40B1-A2DF-437A02F035E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3C3A7D5A-AFB3-47A0-AB77-2AB86F2BC01A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>乌米阿特</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -220,6 +220,41 @@
   </si>
   <si>
     <t>西北地区首府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kautokeino</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挪威</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND NOE00111336
+GSOD 01047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Karasjok
+卡拉绍克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND NO000097250
+GSOD 01065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布伦库勒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔吉克斯坦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 38956</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -860,24 +895,48 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">

--- a/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
+++ b/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AC5C83-030E-40B1-A2DF-437A02F035E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED8BE45-ADC4-4954-87AD-5AE3892C94D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3C3A7D5A-AFB3-47A0-AB77-2AB86F2BC01A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>乌米阿特</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,6 +255,59 @@
   </si>
   <si>
     <t>GSOD 38956</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥地利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SONNBLICK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND AU000015410
+GSOD 11146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19世纪开始
+海拔3109</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snag A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>育空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mayo A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND CA002100700
+GSOD 71965</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND CA002101000
+GSOD 71969199999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月均温(高低平均)CA官网可下载
+Monthly Climate Summaries</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +413,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -399,6 +452,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
@@ -940,25 +996,55 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="A15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="A16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="6"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="A17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
